--- a/output/pdf_financials_xlsx/AUMB.xlsx
+++ b/output/pdf_financials_xlsx/AUMB.xlsx
@@ -3298,22 +3298,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>130.106</v>
+        <v>130.441</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>130.106</v>
+        <v>130.673</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>130.106</v>
+        <v>131.232</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>130.106</v>
+        <v>1.423</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.465</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.597</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -6578,7 +6578,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -7114,7 +7118,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -7608,7 +7616,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -7898,7 +7910,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -8356,7 +8372,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AUMB.xlsx
+++ b/output/pdf_financials_xlsx/AUMB.xlsx
@@ -770,10 +770,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="13">
@@ -1267,10 +1267,10 @@
         <v>-51.193</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-33.108</v>
+        <v>-33.115</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.835</v>
+        <v>-7.991</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-8.766</v>
@@ -1282,10 +1282,10 @@
         <v>-2.006</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.796</v>
+        <v>-4.818</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-25.322</v>
+        <v>-25.493</v>
       </c>
     </row>
     <row r="28">
@@ -1329,10 +1329,10 @@
         <v>-51.193</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-33.108</v>
+        <v>-33.115</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.835</v>
+        <v>-7.991</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-8.766</v>
@@ -1344,10 +1344,10 @@
         <v>-2.006</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.796</v>
+        <v>-4.818</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-25.322</v>
+        <v>-25.493</v>
       </c>
     </row>
     <row r="30">
@@ -1360,10 +1360,10 @@
         <v>-121.3852136387348</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-184.0048907908631</v>
+        <v>-184.0437948090924</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-63.80293159609121</v>
+        <v>-65.07328990228012</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-90.67963173683667</v>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="125">
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="126">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -9804,7 +9804,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -14520,7 +14524,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -16692,7 +16696,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -18012,7 +18016,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUMB.xlsx
+++ b/output/pdf_financials_xlsx/AUMB.xlsx
@@ -624,16 +624,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.114</v>
+        <v>0.271</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.048</v>
+        <v>0.184</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.277</v>
+        <v>0.353</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.641</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="8">
@@ -717,16 +717,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.909</v>
+        <v>3.066</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.182</v>
+        <v>1.318</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.768</v>
+        <v>1.844</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>5.588</v>
+        <v>5.748</v>
       </c>
     </row>
     <row r="11">
@@ -2414,25 +2414,25 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.717</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.602</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.525</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.671</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>5.389</v>
       </c>
     </row>
     <row r="65">
@@ -2507,25 +2507,25 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.317</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.475</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="68">
@@ -13932,7 +13932,11 @@
           <t>Directors fees 16</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -15110,7 +15114,11 @@
           <t>Director fees 16</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -16086,7 +16094,11 @@
           <t>Director fees 15</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
